--- a/rules/CORE-000468/positive/01/data/unit-test-coreid-CG0276-positive 1.xlsx
+++ b/rules/CORE-000468/positive/01/data/unit-test-coreid-CG0276-positive 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QF\CORE\core-contributor\rules\CORE-000468\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D72F5F8-EDDA-49B2-9864-F6C93CD01655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E30361-EBB4-47A5-B8E3-B02251DD7B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -702,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -718,6 +718,7 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2228,13 +2229,14 @@
       <c r="B46" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="6">
-        <v>1</v>
-      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7"/>
       <c r="E46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G46" s="6" t="s">
@@ -2418,13 +2420,14 @@
       <c r="B53" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="6">
-        <v>1</v>
-      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7"/>
       <c r="E53" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="5" t="s">
         <v>191</v>
       </c>
       <c r="G53" s="6" t="s">
